--- a/per-stock/CRM/financials.xlsx
+++ b/per-stock/CRM/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>141940506624</v>
+        <v>124307816448</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>168295727104</v>
+        <v>155018821632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.216389</v>
+        <v>17.56713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.632467</v>
+        <v>9.795158000000001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.418194</v>
+        <v>2.9024215</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -606,7 +615,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.77676004</v>
+        <v>0.77643996</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -621,7 +630,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.19239001</v>
+        <v>0.218</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -636,7 +645,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.17958</v>
+        <v>0.18733</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -651,7 +660,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.123959996</v>
+        <v>0.16908</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -666,7 +675,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.121</v>
+        <v>0.133</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -681,7 +690,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9564999680</v>
+        <v>11836999680</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -696,7 +705,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17710999552</v>
+        <v>42547998720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16366999552</v>
+        <v>14661000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>818053744</v>
+        <v>819000000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>173.51</v>
+        <v>151.78</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D47</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C47</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B47</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B50:E50)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D45</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C45</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B45</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B48:E48)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D33</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C33</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B33</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B37:E37)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1776,13 +2256,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1801,27 +2281,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
         </is>
       </c>
     </row>
@@ -1832,19 +2312,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>109940000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>136843607.305936</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>510000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>440000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-21780000</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>-28450704.225352</v>
       </c>
     </row>
     <row r="3">
@@ -1854,19 +2334,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.260654</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.17</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.22</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0.22</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.140845</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="4">
@@ -1876,19 +2356,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>3545000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>2750000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>3296000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>3151000000</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>2920000000</v>
-      </c>
       <c r="F4" s="3" t="n">
-        <v>3197000000</v>
+        <v>2984000000</v>
       </c>
     </row>
     <row r="5">
@@ -1898,19 +2378,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>478000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>525000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-99000000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-202000000</v>
       </c>
     </row>
     <row r="6">
@@ -1920,19 +2400,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>478000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>525000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-99000000</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-202000000</v>
       </c>
     </row>
     <row r="7">
@@ -1942,19 +2422,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>2107000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>1943000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>2086000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>1887000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>1541000000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1708000000</v>
       </c>
     </row>
     <row r="8">
@@ -1964,19 +2444,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>985000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>1120000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>851000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>817000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>843000000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>877000000</v>
       </c>
     </row>
     <row r="9">
@@ -1986,19 +2466,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>4472000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>2508000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>2255000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>2242000000</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>2265000000</v>
-      </c>
       <c r="F9" s="3" t="n">
-        <v>2217000000</v>
+        <v>3920000000</v>
       </c>
     </row>
     <row r="10">
@@ -2008,19 +2488,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>4023000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>3275000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>3299000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>3153000000</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>2821000000</v>
-      </c>
       <c r="F10" s="3" t="n">
-        <v>2995000000</v>
+        <v>2885000000</v>
       </c>
     </row>
     <row r="11">
@@ -2030,723 +2510,851 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>3038000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>2155000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>2448000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>2336000000</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>1978000000</v>
-      </c>
       <c r="F11" s="3" t="n">
-        <v>2118000000</v>
+        <v>2042000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Normalized Income</t>
+          <t>Net Interest Income</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1554843607.305936</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>2083510000</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>1885440000</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>1618220000</v>
-      </c>
+        <v>-317000000</v>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n">
-        <v>1881549295.774648</v>
+        <v>-68000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Net Income From Continuing And Discontinued Operation</t>
+          <t>Interest Expense</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1943000000</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>2086000000</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>1887000000</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>1541000000</v>
-      </c>
+        <v>317000000</v>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n">
-        <v>1708000000</v>
+        <v>68000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Total Expenses</t>
+          <t>Normalized Income</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>9046000000</v>
+        <v>1738940000</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>7811000000</v>
+        <v>1554843607.305936</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>7900000000</v>
+        <v>2083510000</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7851000000</v>
+        <v>1885440000</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>7875000000</v>
+        <v>1618220000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Total Operating Income As Reported</t>
+          <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1869000000</v>
+        <v>2107000000</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2188000000</v>
+        <v>1943000000</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2332000000</v>
+        <v>2086000000</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1942000000</v>
+        <v>1887000000</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1820000000</v>
+        <v>1541000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Diluted Average Shares</t>
+          <t>Total Expenses</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>940000000</v>
+        <v>11276000000</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>952000000</v>
+        <v>9046000000</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>962000000</v>
+        <v>7811000000</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>970000000</v>
+        <v>7900000000</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>974000000</v>
+        <v>10116000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Basic Average Shares</t>
+          <t>Total Operating Income As Reported</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>935000000</v>
+        <v>2347000000</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>948000000</v>
+        <v>1869000000</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>956000000</v>
+        <v>2188000000</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>960000000</v>
+        <v>2332000000</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>959000000</v>
+        <v>1942000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Diluted EPS</t>
+          <t>Diluted Average Shares</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2.07</v>
+        <v>871000000</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2.19</v>
+        <v>940000000</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1.96</v>
+        <v>952000000</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1.59</v>
+        <v>962000000</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.75</v>
+        <v>970000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Basic EPS</t>
+          <t>Basic Average Shares</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>2.08</v>
+        <v>868000000</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2.2</v>
+        <v>935000000</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1.97</v>
+        <v>948000000</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1.61</v>
+        <v>956000000</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.78</v>
+        <v>960000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Diluted NI Availto Com Stockholders</t>
+          <t>Diluted EPS</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1943000000</v>
+        <v>2.42</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2086000000</v>
+        <v>2.07</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1887000000</v>
+        <v>2.19</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1541000000</v>
+        <v>1.96</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1708000000</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Net Income Common Stockholders</t>
+          <t>Basic EPS</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1943000000</v>
+        <v>2.43</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>2086000000</v>
+        <v>2.08</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1887000000</v>
+        <v>2.2</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1541000000</v>
+        <v>1.97</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1708000000</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Net Income</t>
+          <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>2107000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>1943000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>2086000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>1887000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>1541000000</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>1708000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Net Income Including Noncontrolling Interests</t>
+          <t>Net Income Common Stockholders</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>2107000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>1943000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>2086000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>1887000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>1541000000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>1708000000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Net Income Continuous Operations</t>
+          <t>Net Income</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>2107000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>1943000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>2086000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>1887000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>1541000000</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>1708000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tax Provision</t>
+          <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>685000000</v>
+        <v>2107000000</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>426000000</v>
+        <v>1943000000</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>519000000</v>
+        <v>2086000000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>433000000</v>
+        <v>1887000000</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>280000000</v>
+        <v>1541000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pretax Income</t>
+          <t>Net Income Continuous Operations</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2628000000</v>
+        <v>2107000000</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2512000000</v>
+        <v>1943000000</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2406000000</v>
+        <v>2086000000</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1974000000</v>
+        <v>1887000000</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1988000000</v>
+        <v>1541000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Other Income Expense</t>
+          <t>Tax Provision</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>473000000</v>
+        <v>614000000</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>64000000</v>
+        <v>685000000</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>70000000</v>
+        <v>426000000</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4000000</v>
+        <v>519000000</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-130000000</v>
+        <v>433000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Other Non Operating Income Expenses</t>
+          <t>Pretax Income</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-52000000</v>
+        <v>2721000000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>61000000</v>
+        <v>2628000000</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>68000000</v>
+        <v>2512000000</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>95000000</v>
+        <v>2406000000</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>72000000</v>
+        <v>1974000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Special Income Charges</t>
+          <t>Other Income Expense</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-480000000</v>
+        <v>611000000</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-429000000</v>
+        <v>473000000</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-90000000</v>
+        <v>64000000</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-83000000</v>
+        <v>70000000</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-448000000</v>
+        <v>64000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Write Off</t>
+          <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>194000000</v>
+        <v>133000000</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>169000000</v>
+        <v>-52000000</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>86000000</v>
+        <v>61000000</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>47000000</v>
+        <v>68000000</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>150000000</v>
+        <v>163000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Restructuring And Mergern Acquisition</t>
+          <t>Special Income Charges</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>286000000</v>
+        <v>-199000000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>260000000</v>
+        <v>-480000000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>4000000</v>
+        <v>-429000000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>36000000</v>
+        <v>-90000000</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>298000000</v>
+        <v>-83000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gain On Sale Of Security</t>
+          <t>Write Off</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>1005000000</v>
+        <v>119000000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>432000000</v>
+        <v>194000000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>92000000</v>
+        <v>169000000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-16000000</v>
+        <v>86000000</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>246000000</v>
+        <v>47000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Operating Income</t>
+          <t>Restructuring And Mergern Acquisition</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>2155000000</v>
+        <v>80000000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2448000000</v>
+        <v>286000000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2336000000</v>
+        <v>260000000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1978000000</v>
+        <v>4000000</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2118000000</v>
+        <v>36000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Operating Expense</t>
+          <t>Gain On Sale Of Security</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>6538000000</v>
+        <v>677000000</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>5556000000</v>
+        <v>1005000000</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>5658000000</v>
+        <v>432000000</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>5586000000</v>
+        <v>92000000</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>5658000000</v>
+        <v>-16000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Research And Development</t>
+          <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>1619000000</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>1433000000</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>1481000000</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>1460000000</v>
-      </c>
+        <v>-317000000</v>
+      </c>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n">
-        <v>1420000000</v>
+        <v>-68000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Selling General And Administration</t>
+          <t>Interest Expense Non Operating</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>3924000000</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>4123000000</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>4177000000</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>4126000000</v>
-      </c>
+        <v>317000000</v>
+      </c>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n">
-        <v>4238000000</v>
+        <v>68000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Selling And Marketing Expense</t>
+          <t>Operating Income</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>3022000000</v>
+        <v>2427000000</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>3456000000</v>
+        <v>2155000000</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>3443000000</v>
+        <v>2448000000</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>3429000000</v>
+        <v>2336000000</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>3471000000</v>
+        <v>1978000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>General And Administrative Expense</t>
+          <t>Operating Expense</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>902000000</v>
+        <v>6136000000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>667000000</v>
+        <v>6538000000</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>734000000</v>
+        <v>5556000000</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>697000000</v>
+        <v>5658000000</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>767000000</v>
+        <v>5586000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Other Gand A</t>
+          <t>Depreciation Amortization Depletion Income Statement</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>902000000</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>667000000</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>734000000</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>697000000</v>
-      </c>
+        <v>317000000</v>
+      </c>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n">
-        <v>767000000</v>
+        <v>233000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Depreciation And Amortization In Income Statement</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>8693000000</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>8004000000</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>7994000000</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>7564000000</v>
-      </c>
+        <v>317000000</v>
+      </c>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n">
-        <v>7776000000</v>
+        <v>233000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cost Of Revenue</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>2508000000</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>2255000000</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>2242000000</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>2265000000</v>
-      </c>
+        <v>317000000</v>
+      </c>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n">
-        <v>2217000000</v>
+        <v>233000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
+          <t>Amortization Of Intangibles Income Statement</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>11201000000</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>10259000000</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>10236000000</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>9829000000</v>
-      </c>
+        <v>317000000</v>
+      </c>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n">
-        <v>9993000000</v>
+        <v>233000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Research And Development</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>1627000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1619000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1433000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1481000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1460000000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Selling General And Administration</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>4192000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>3924000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>4123000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>4177000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>3893000000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Selling And Marketing Expense</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>3452000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>3022000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>3456000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>3443000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>3196000000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>General And Administrative Expense</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>740000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>902000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>667000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>734000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>697000000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Other Gand A</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>740000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>902000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>667000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>734000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>697000000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>8563000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>8693000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>8004000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>7994000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>7564000000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cost Of Revenue</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>5140000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>2508000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>2255000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>2242000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>4530000000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>11133000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>11201000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>10259000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>10236000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>9829000000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
+      <c r="B51" s="3" t="n">
+        <v>11133000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>11201000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>10259000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>10236000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>9829000000</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>9993000000</v>
       </c>
     </row>
   </sheetData>
@@ -2754,7 +3362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4156,7 +4764,1593 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>258000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>144000000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>127000000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>112000000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>104000000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>819000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>929000000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>942000000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>955000000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>958000000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1077000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1073000000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1069000000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1067000000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1062000000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>30345000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>7112000000</v>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n">
+        <v>435000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>41884000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>17176000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>11139000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>11237000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>11369000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-31706000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-5614000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>4073000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>6221000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>5352000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>73515000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>73581000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>68459000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>69764000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>69101000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-5889000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-8896000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-347000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2799000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1670000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-31706000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-5614000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>4073000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>6221000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>5352000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2604000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>2737000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2701000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2801000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2934000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>34235000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>59142000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>60021000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>61328000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>60666000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>73515000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>69581000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>68459000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>69764000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>69101000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>34235000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>59142000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>60021000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>61328000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>60666000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>34235000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>59142000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>60021000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>61328000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>60666000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>395000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>313000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>154000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-130000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>395000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>313000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>154000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-130000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>55028000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>32228000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>28255000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>24408000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>22199000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>23954000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>22221000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>20673000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>18987000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>17504000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>64913000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>68835000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>67448000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>66701000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>65490000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>72445000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>53163000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>35123000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>36245000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>37944000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>44943000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>16045000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>13713000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>13713000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>13748000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>3616000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>3417000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>3138000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>3056000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>2972000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>41327000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>12628000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>10575000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>10657000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>10776000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>2047000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2189000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>2137000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>2221000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>2341000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>39280000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>10439000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>8438000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>8436000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>8435000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>27502000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>37118000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>21410000000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>22532000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>24196000000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>20363000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>24317000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>14996000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>16555000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>17799000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>20363000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>24317000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>14996000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>16555000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>17799000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>557000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>4548000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>564000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>580000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>593000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>557000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>548000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>564000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>580000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>593000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Line Of Credit</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>6582000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>8253000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>5850000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>5397000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>5804000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>106680000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>112305000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>95144000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>97573000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>98610000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>85067000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>84083000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>74081000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>72242000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>72744000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>3395000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>3628000000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>4334000000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>4602000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>4887000000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>2920000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>2985000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>2293000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>2266000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>2342000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n">
+        <v>4334000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>4602000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>4887000000</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>4770000000</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>7772000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>7591000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>6410000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>5085000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>4941000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Other Investments</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>44000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>44000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>7732000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>7547000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>6366000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>5040000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>4905000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Held To Maturity Securities</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>41000000</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>93000000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>7732000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>7547000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>6366000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>5040000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>4905000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>65941000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>64756000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>55948000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>55107000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>55314000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>6650000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>6815000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>3491000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>3669000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>4033000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>59291000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>57941000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>52457000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>51438000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>51281000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>5039000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>5123000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>5096000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>5182000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>5260000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n">
+        <v>-3703000000</v>
+      </c>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n">
+        <v>-3682000000</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>5039000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>8826000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>5096000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>5182000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>5260000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n">
+        <v>1617000000</v>
+      </c>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n">
+        <v>1556000000</v>
+      </c>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>5039000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>2003000000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>5096000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>5182000000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>5260000000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n">
+        <v>4349000000</v>
+      </c>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n">
+        <v>4577000000</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n">
+        <v>492000000</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n">
+        <v>357000000</v>
+      </c>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n">
+        <v>293000000</v>
+      </c>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>21613000000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>28222000000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>21063000000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>25331000000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>25866000000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>2631000000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>2243000000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>2431000000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>2501000000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>2180000000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>2065000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>2075000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>1835000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>1862000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1924000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>5080000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>14339000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>5474000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>5596000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>4354000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>5080000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>14339000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>5474000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>5596000000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>4354000000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>11837000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>9565000000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>11323000000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>15372000000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>17408000000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>2902000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>2238000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>2345000000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>5007000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>6480000000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>8935000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>7327000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>8978000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>10365000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>10928000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5230,13 +7424,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5256,32 +7450,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
         </is>
       </c>
     </row>
@@ -5292,19 +7486,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>6556000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>5323000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>2177000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>605000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>6297000000</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>3816000000</v>
       </c>
       <c r="G2" s="3" t="n"/>
     </row>
@@ -5315,19 +7509,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-27248000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-3937000000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-3801000000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-2225000000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-2633000000</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>-76000000</v>
       </c>
       <c r="G3" s="3" t="n"/>
     </row>
@@ -5338,1036 +7532,1072 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-130000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-146000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-160000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-99000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-179000000</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>-98000000</v>
       </c>
       <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Capital Expenditure</t>
+          <t>Issuance Of Debt</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-141000000</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>-139000000</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>-135000000</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>-179000000</v>
-      </c>
+        <v>24842000000</v>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n">
-        <v>-154000000</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Interest Paid Supplemental Data</t>
+          <t>Capital Expenditure</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>133000000</v>
+        <v>-145000000</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>28000000</v>
+        <v>-141000000</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>87000000</v>
+        <v>-139000000</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>28000000</v>
+        <v>-135000000</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>87000000</v>
+        <v>-179000000</v>
       </c>
       <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Income Tax Paid Supplemental Data</t>
+          <t>Interest Paid Supplemental Data</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>159000000</v>
+        <v>87000000</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>133000000</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>891000000</v>
+        <v>28000000</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>99000000</v>
+        <v>87000000</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>673000000</v>
+        <v>28000000</v>
       </c>
       <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>End Cash Position</t>
+          <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>7327000000</v>
+        <v>239000000</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>8978000000</v>
+        <v>159000000</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10365000000</v>
+        <v>133000000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>10928000000</v>
+        <v>891000000</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>8848000000</v>
+        <v>99000000</v>
       </c>
       <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Beginning Cash Position</t>
+          <t>End Cash Position</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>8935000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>7327000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
         <v>8978000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>10365000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>10928000000</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>8848000000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>7997000000</v>
       </c>
       <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Effect Of Exchange Rate Changes</t>
+          <t>Beginning Cash Position</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4000000</v>
+        <v>7327000000</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>22000000</v>
+        <v>8978000000</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>35000000</v>
+        <v>10365000000</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>91000000</v>
+        <v>10928000000</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-110000000</v>
+        <v>8848000000</v>
       </c>
       <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Changes In Cash</t>
+          <t>Effect Of Exchange Rate Changes</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-1655000000</v>
+        <v>11000000</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-1409000000</v>
+        <v>4000000</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-598000000</v>
+        <v>22000000</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1989000000</v>
+        <v>35000000</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>961000000</v>
+        <v>91000000</v>
       </c>
       <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Financing Cash Flow</t>
+          <t>Changes In Cash</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1588000000</v>
+        <v>1597000000</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-4244000000</v>
+        <v>-1655000000</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-2503000000</v>
+        <v>-1409000000</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-2920000000</v>
+        <v>-598000000</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-73000000</v>
+        <v>1989000000</v>
       </c>
       <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Financing Activities</t>
+          <t>Financing Cash Flow</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-2921000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>1588000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-4244000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-2503000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-2920000000</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>-73000000</v>
       </c>
       <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Net Other Financing Charges</t>
+          <t>Cash Flow From Continuing Financing Activities</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-212000000</v>
+        <v>-2921000000</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-127000000</v>
+        <v>1588000000</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-12000000</v>
-      </c>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
+        <v>-4244000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-2503000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-2920000000</v>
+      </c>
       <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Proceeds From Stock Option Exercised</t>
+          <t>Net Other Financing Charges</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>274000000</v>
+        <v>-250000000</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>239000000</v>
+        <v>-212000000</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>232000000</v>
+        <v>-127000000</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>294000000</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>484000000</v>
-      </c>
+        <v>-12000000</v>
+      </c>
+      <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cash Dividends Paid</t>
+          <t>Proceeds From Stock Option Exercised</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-391000000</v>
+        <v>230000000</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-395000000</v>
+        <v>274000000</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-399000000</v>
+        <v>239000000</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-402000000</v>
+        <v>232000000</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-383000000</v>
+        <v>294000000</v>
       </c>
       <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Common Stock Dividend Paid</t>
+          <t>Cash Dividends Paid</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-365000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-391000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-395000000</v>
       </c>
-      <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n">
+        <v>-399000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>-402000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-383000000</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>-382000000</v>
-      </c>
+      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Net Common Stock Issuance</t>
+          <t>Common Stock Dividend Paid</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-3937000000</v>
+        <v>-365000000</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-3801000000</v>
+        <v>-391000000</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-2225000000</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>-2633000000</v>
-      </c>
+        <v>-395000000</v>
+      </c>
+      <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n">
-        <v>-76000000</v>
-      </c>
-      <c r="G18" s="3" t="n"/>
+        <v>-402000000</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-383000000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Common Stock Payments</t>
+          <t>Net Common Stock Issuance</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-27248000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-3937000000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-3801000000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-2225000000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-2633000000</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>-76000000</v>
       </c>
       <c r="G19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Net Issuance Payments Of Debt</t>
+          <t>Common Stock Payments</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5854000000</v>
+        <v>-27248000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-160000000</v>
+        <v>-3937000000</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-99000000</v>
+        <v>-3801000000</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-179000000</v>
+        <v>-2225000000</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-98000000</v>
+        <v>-2633000000</v>
       </c>
       <c r="G20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Net Long Term Debt Issuance</t>
+          <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>24712000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>5854000000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-160000000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-99000000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-179000000</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>-98000000</v>
       </c>
       <c r="G21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Long Term Debt Payments</t>
+          <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-146000000</v>
+        <v>24712000000</v>
       </c>
       <c r="C22" s="3" t="n">
+        <v>5854000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>-160000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-99000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-179000000</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>-98000000</v>
       </c>
       <c r="G22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Investing Cash Flow</t>
+          <t>Long Term Debt Payments</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-8707000000</v>
+        <v>-130000000</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>519000000</v>
+        <v>-146000000</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1165000000</v>
+        <v>-160000000</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-1567000000</v>
+        <v>-99000000</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-2936000000</v>
+        <v>-179000000</v>
       </c>
       <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Investing Activities</t>
+          <t>Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-8707000000</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>519000000</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>1165000000</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-1567000000</v>
-      </c>
+        <v>24842000000</v>
+      </c>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n">
-        <v>-2936000000</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Net Investment Purchase And Sale</t>
+          <t>Investing Cash Flow</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-330000000</v>
+        <v>-2183000000</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1636000000</v>
+        <v>-8707000000</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1354000000</v>
+        <v>519000000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-1388000000</v>
+        <v>1165000000</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-565000000</v>
+        <v>-1567000000</v>
       </c>
       <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sale Of Investment</t>
+          <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>375000000</v>
+        <v>-2183000000</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3125000000</v>
+        <v>-8707000000</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2646000000</v>
+        <v>519000000</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>847000000</v>
+        <v>1165000000</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1438000000</v>
+        <v>-1567000000</v>
       </c>
       <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Purchase Of Investment</t>
+          <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-705000000</v>
+        <v>-586000000</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1489000000</v>
+        <v>-330000000</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1292000000</v>
+        <v>1636000000</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2235000000</v>
+        <v>1354000000</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2003000000</v>
+        <v>-1388000000</v>
       </c>
       <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Net Business Purchase And Sale</t>
+          <t>Sale Of Investment</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-8236000000</v>
+        <v>828000000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-978000000</v>
+        <v>375000000</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-54000000</v>
+        <v>3125000000</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>2646000000</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>-2217000000</v>
+        <v>847000000</v>
       </c>
       <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Purchase Of Business</t>
+          <t>Purchase Of Investment</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-8236000000</v>
+        <v>-1414000000</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-978000000</v>
+        <v>-705000000</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-54000000</v>
+        <v>-1489000000</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0</v>
+        <v>-1292000000</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2217000000</v>
+        <v>-2235000000</v>
       </c>
       <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Capital Expenditure Reported</t>
+          <t>Net Business Purchase And Sale</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-141000000</v>
+        <v>-1452000000</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-139000000</v>
+        <v>-8236000000</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-135000000</v>
+        <v>-978000000</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-179000000</v>
+        <v>-54000000</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-154000000</v>
+        <v>0</v>
       </c>
       <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Operating Cash Flow</t>
+          <t>Purchase Of Business</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5464000000</v>
+        <v>-1452000000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2316000000</v>
+        <v>-8236000000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>740000000</v>
+        <v>-978000000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>6476000000</v>
+        <v>-54000000</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3970000000</v>
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Operating Activities</t>
+          <t>Capital Expenditure Reported</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5464000000</v>
+        <v>-145000000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>2316000000</v>
+        <v>-141000000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>740000000</v>
+        <v>-139000000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>6476000000</v>
+        <v>-135000000</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>3970000000</v>
+        <v>-179000000</v>
       </c>
       <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Change In Working Capital</t>
+          <t>Operating Cash Flow</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>1569000000</v>
+        <v>6701000000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-1725000000</v>
+        <v>5464000000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-3295000000</v>
+        <v>2316000000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>2670000000</v>
+        <v>740000000</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>151000000</v>
+        <v>6476000000</v>
       </c>
       <c r="G33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Change In Other Working Capital</t>
+          <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>7179000000</v>
+        <v>6701000000</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-2107000000</v>
+        <v>5464000000</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>-1650000000</v>
+        <v>2316000000</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-3309000000</v>
+        <v>740000000</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>6123000000</v>
+        <v>6476000000</v>
       </c>
       <c r="G34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Change In Other Current Liabilities</t>
+          <t>Change In Working Capital</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-152000000</v>
+        <v>2726000000</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-137000000</v>
+        <v>1569000000</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-154000000</v>
+        <v>-1725000000</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-124000000</v>
+        <v>-3295000000</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-161000000</v>
+        <v>2670000000</v>
       </c>
       <c r="G35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Change In Payables And Accrued Expense</t>
+          <t>Change In Other Working Capital</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>2238000000</v>
+        <v>-4508000000</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>7179000000</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-217000000</v>
+        <v>-2107000000</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-1007000000</v>
+        <v>-1650000000</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1592000000</v>
+        <v>-3309000000</v>
       </c>
       <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Change In Payable</t>
+          <t>Change In Other Current Liabilities</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>2238000000</v>
-      </c>
-      <c r="C37" s="3" t="n"/>
+        <v>-138000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>-152000000</v>
+      </c>
       <c r="D37" s="3" t="n">
-        <v>-217000000</v>
+        <v>-137000000</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-1007000000</v>
+        <v>-154000000</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1592000000</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>32000000</v>
-      </c>
+        <v>-124000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Change In Account Payable</t>
+          <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-1897000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>2238000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>-217000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-1007000000</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>1592000000</v>
       </c>
       <c r="G38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Change In Prepaid Assets</t>
+          <t>Change In Payable</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>936000000</v>
+        <v>-1897000000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>396000000</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>-32000000</v>
-      </c>
+        <v>2238000000</v>
+      </c>
+      <c r="D39" s="3" t="n"/>
       <c r="E39" s="3" t="n">
-        <v>-481000000</v>
+        <v>-217000000</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-232000000</v>
-      </c>
-      <c r="G39" s="3" t="n"/>
+        <v>-1007000000</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1592000000</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Change In Receivables</t>
+          <t>Change In Account Payable</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-8632000000</v>
+        <v>-1897000000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>123000000</v>
+        <v>2238000000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-1242000000</v>
+        <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>7591000000</v>
+        <v>-217000000</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-7171000000</v>
+        <v>-1007000000</v>
       </c>
       <c r="G40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Changes In Account Receivables</t>
+          <t>Change In Prepaid Assets</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-8632000000</v>
+        <v>-162000000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>123000000</v>
+        <v>936000000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-1242000000</v>
+        <v>396000000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>7591000000</v>
+        <v>-32000000</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-7171000000</v>
+        <v>-481000000</v>
       </c>
       <c r="G41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Other Non Cash Items</t>
+          <t>Change In Receivables</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>560000000</v>
+        <v>9431000000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>548000000</v>
+        <v>-8632000000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>544000000</v>
+        <v>123000000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>545000000</v>
+        <v>-1242000000</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>527000000</v>
+        <v>7591000000</v>
       </c>
       <c r="G42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Stock Based Compensation</t>
+          <t>Changes In Account Receivables</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>1083000000</v>
+        <v>9431000000</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>819000000</v>
+        <v>-8632000000</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>793000000</v>
+        <v>123000000</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>814000000</v>
+        <v>-1242000000</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>803000000</v>
+        <v>7591000000</v>
       </c>
       <c r="G43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
+          <t>Other Non Cash Items</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>1120000000</v>
+        <v>584000000</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>851000000</v>
+        <v>560000000</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>817000000</v>
+        <v>548000000</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>843000000</v>
+        <v>544000000</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>877000000</v>
+        <v>545000000</v>
       </c>
       <c r="G44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Stock Based Compensation</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>1120000000</v>
+        <v>857000000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>851000000</v>
+        <v>1083000000</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>817000000</v>
+        <v>819000000</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>843000000</v>
+        <v>793000000</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>877000000</v>
+        <v>814000000</v>
       </c>
       <c r="G45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
+          <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>-811000000</v>
+        <v>985000000</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>-263000000</v>
+        <v>1120000000</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>-6000000</v>
+        <v>851000000</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>63000000</v>
+        <v>817000000</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>-96000000</v>
+        <v>843000000</v>
       </c>
       <c r="G46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Gain Loss On Investment Securities</t>
+          <t>Depreciation And Amortization</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>-811000000</v>
+        <v>985000000</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>-263000000</v>
+        <v>1120000000</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>-6000000</v>
+        <v>851000000</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>63000000</v>
+        <v>817000000</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-96000000</v>
+        <v>843000000</v>
       </c>
       <c r="G47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>Operating Gains Losses</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>-558000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>-811000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>-263000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Gain Loss On Investment Securities</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>-558000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>-811000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>-263000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n">
+      <c r="B50" s="3" t="n">
+        <v>2107000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>1943000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>2086000000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>1887000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>1541000000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>1708000000</v>
-      </c>
-      <c r="G48" s="3" t="n"/>
+      <c r="G50" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
